--- a/02_DIA_inicio_2026_analisis_assets/rbd_9592_escuela-basica-sendero-del-saber_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9592_escuela-basica-sendero-del-saber_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB2720E-9AFF-4A29-9E28-E70B11345538}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03E85324-FB08-4838-8DAE-436D7B5F9FCC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E1F4687-D915-40A4-AC8A-1B2B6C88286E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B10D773C-05E1-4FCA-93F2-4D92E2DB3F73}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2307490D-5640-4B8E-A120-DE06CAD9CA8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6B782D3-50AC-4758-B7FE-3C9A3B8072AF}"/>
 </file>